--- a/artfynd/A 4817-2024 artfynd.xlsx
+++ b/artfynd/A 4817-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121129374</v>
       </c>
       <c r="B2" t="n">
-        <v>91127</v>
+        <v>91137</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>121130914</v>
       </c>
       <c r="B3" t="n">
-        <v>91127</v>
+        <v>91137</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 4817-2024 artfynd.xlsx
+++ b/artfynd/A 4817-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121129374</v>
       </c>
       <c r="B2" t="n">
-        <v>91137</v>
+        <v>91149</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>121130914</v>
       </c>
       <c r="B3" t="n">
-        <v>91137</v>
+        <v>91149</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 4817-2024 artfynd.xlsx
+++ b/artfynd/A 4817-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121129374</v>
       </c>
       <c r="B2" t="n">
-        <v>91149</v>
+        <v>91150</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>121130914</v>
       </c>
       <c r="B3" t="n">
-        <v>91149</v>
+        <v>91150</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 4817-2024 artfynd.xlsx
+++ b/artfynd/A 4817-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121129374</v>
       </c>
       <c r="B2" t="n">
-        <v>91150</v>
+        <v>91153</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>121130914</v>
       </c>
       <c r="B3" t="n">
-        <v>91150</v>
+        <v>91153</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
